--- a/docs/DBS4_Corrections_Register_20260921-dbcd48b8.xlsx
+++ b/docs/DBS4_Corrections_Register_20260921-dbcd48b8.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corrections register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Corrections register'!$A$1:$R$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Corrections register'!$A$1:$U$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R176"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -468,14 +468,17 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,40 +534,55 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ex-deal TOS/PP/ROS clicks</t>
+          <t>90d TOS/PP/ROS clicks (incl. deal)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>PP share</t>
+          <t>PP share 90d</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>TOS clicks/day pre-deal</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TOS clicks/day in deal</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>PP share in deal</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>TOS ceiling</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TOS price now</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TOS price engine</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>TOS price corrected</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Base corrected</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Write kind</t>
         </is>
@@ -610,7 +628,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -619,28 +637,37 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>506/426/198</t>
+          <t>522/461/201</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.377</v>
+        <v>0.389</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3.61</v>
+        <v>2.1</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>3.61</v>
+        <v>0.638</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
+        <v>3.61</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -686,7 +713,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>361</v>
+        <v>229</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -695,104 +722,124 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>115/163/6</t>
+          <t>138/169/6</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.574</v>
+        <v>0.54</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6.46</v>
+        <v>2.7</v>
       </c>
       <c r="N3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q3" s="2" t="n">
         <v>6.69</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="P3" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-Bamboo Sheets Queen Size-[Bamboo|Queen]-(HSV)-Exact-(Ranking)-UD-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>382995705013765</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>target · bamboo sheets queen size</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>STOCK, DEAL, FLOOR</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>115/163/6</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="N4" s="2" t="n">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>BASE-CUT-DEAL, STOCK, DEAL, FLOOR</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>138/169/6</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>6.69</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="3" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -847,28 +894,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>206/667/22</t>
+          <t>211/671/23</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4.59</v>
+        <v>1.3</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q5" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -923,28 +979,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>206/667/22</t>
+          <t>211/671/23</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4.59</v>
+        <v>1.3</v>
       </c>
       <c r="N6" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="T6" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -999,28 +1064,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>206/667/22</t>
+          <t>211/671/23</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.59</v>
+        <v>1.3</v>
       </c>
       <c r="N7" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q7" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="T7" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -1075,28 +1149,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>206/667/22</t>
+          <t>211/671/23</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4.59</v>
+        <v>1.3</v>
       </c>
       <c r="N8" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q8" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="T8" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -1151,28 +1234,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>206/667/22</t>
+          <t>211/671/23</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0.745</v>
+        <v>0.741</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4.59</v>
+        <v>1.3</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q9" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="T9" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -1229,28 +1321,37 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>579/56/272</t>
+          <t>641/57/275</t>
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.18</v>
+        <v>6.7</v>
       </c>
       <c r="N10" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>3.14</v>
       </c>
-      <c r="P10" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1307,28 +1408,37 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R11" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1385,28 +1495,37 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1463,28 +1582,37 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L13" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M13" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1541,28 +1669,37 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1619,28 +1756,37 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1697,28 +1843,37 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M16" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1775,28 +1930,37 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>161/1/641</t>
+          <t>161/1/648</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">
         <v>0.001</v>
       </c>
       <c r="M17" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>3.37</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>1.98</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -1848,109 +2012,129 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>HISTORY, CLIMB-MIX-FIRST, PREMIUM-UNFUNDED, MOD-CAP, PLACEMENT-READ, DEAL, FLOOR, CEILINGED</t>
+          <t>HISTORY, PREMIUM-UNFUNDED, MOD-CAP, PLACEMENT-READ, DEAL, FLOOR, CEILINGED</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>65/307/8</t>
+          <t>95/307/8</t>
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.749</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>3.97</v>
+        <v>0.7</v>
       </c>
       <c r="N18" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>7.61</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="R18" s="3" t="n">
         <v>7.62</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Q18" s="3" t="n">
+      <c r="S18" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>descent to a named point: the TOS ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>DBS4-SP-Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>405247460877728</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>bid</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>target · bamboo cooling sheets</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>BASE-CUT-DEAL, DEAL, FLOOR</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>95/307/8</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>descent to a named point: the TOS ceiling</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>DBS4-SP-Bamboo Cooling Sheets-(MSV)-Exact-(Ranking)-DO-BAMBOO-QUEEN-WHITE</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>405247460877728</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>bid</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>target · bamboo cooling sheets</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>DEAL, FLOOR</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>65/307/8</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>7.61</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="R19" s="3" t="n">
         <v>7.62</v>
       </c>
-      <c r="P19" s="2" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="S19" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -1996,7 +2180,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -2005,28 +2189,37 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>97/56/12</t>
+          <t>113/63/12</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3.95</v>
+        <v>0.7</v>
       </c>
       <c r="N20" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q20" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>5.45</v>
       </c>
-      <c r="P20" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q20" s="2" t="n">
+      <c r="S20" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T20" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="R20" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2081,28 +2274,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>97/56/12</t>
+          <t>113/63/12</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3.95</v>
+        <v>0.7</v>
       </c>
       <c r="N21" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q21" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>5.45</v>
       </c>
-      <c r="P21" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q21" s="2" t="n">
+      <c r="S21" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T21" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="R21" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2157,28 +2359,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>97/56/12</t>
+          <t>113/63/12</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3.95</v>
+        <v>0.7</v>
       </c>
       <c r="N22" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="Q22" s="2" t="n">
         <v>4.96</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>5.45</v>
       </c>
-      <c r="P22" s="2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Q22" s="2" t="n">
+      <c r="S22" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T22" s="2" t="n">
         <v>0.88</v>
       </c>
-      <c r="R22" s="2" t="inlineStr">
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2235,256 +2446,298 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>19/5/0</t>
+          <t>37/6/1</t>
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.208</v>
+        <v>0.136</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>5.16</v>
+        <v>0.6</v>
       </c>
       <c r="N23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Q23" s="3" t="n">
         <v>7.45</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="R23" s="3" t="n">
         <v>7.45</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
+      <c r="S23" s="3" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-King Size Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>366160209689664</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>tos</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>703</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>CLIMB-MIX-FIRST, PUSH-UNPROVEN, MOD-CAP, PLACEMENT-READ, DEAL, CEILINGED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>98/270/13</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N24" s="2" t="n">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>PUSH-UNPROVEN, MOD-CAP, PLACEMENT-READ, DEAL, CEILINGED</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>122/270/13</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q24" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="R24" s="3" t="n">
         <v>9.35</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="S24" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="Q24" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
+      <c r="T24" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-King Size Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>366160209689664</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>target · king size bamboo sheets set</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>DEAL</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>98/270/13</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N25" s="2" t="n">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>BASE-CUT-DEAL, DEAL</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>122/270/13</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="R25" s="3" t="n">
         <v>9.35</v>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="S25" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="Q25" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
+      <c r="T25" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-King Size Bamboo Sheet Sets-(VLSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>366160209689664</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>target · king size bamboo sheet sets</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>DEAL</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>98/270/13</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="N26" s="2" t="n">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>BASE-CUT-DEAL, DEAL</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>122/270/13</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="R26" s="3" t="n">
         <v>9.35</v>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="S26" s="3" t="n">
         <v>9.33</v>
       </c>
-      <c r="Q26" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="T26" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -2541,28 +2794,37 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>17/0/3</t>
+          <t>22/0/3</t>
         </is>
       </c>
       <c r="L27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>4.64</v>
+        <v>0.5</v>
       </c>
       <c r="N27" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>9.76</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="R27" s="3" t="n">
         <v>9.76</v>
       </c>
-      <c r="P27" s="3" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+      <c r="S27" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="T27" s="3" t="n">
         <v>2.38</v>
       </c>
-      <c r="R27" s="3" t="inlineStr">
+      <c r="U27" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2619,28 +2881,37 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N28" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O28" s="3" t="n">
+      <c r="R28" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P28" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q28" s="3" t="n">
+      <c r="S28" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="U28" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2686,7 +2957,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2695,28 +2966,37 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N29" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q29" s="2" t="n">
         <v>7.8</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="R29" s="2" t="n">
         <v>7.81</v>
       </c>
-      <c r="P29" s="2" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q29" s="2" t="n">
+      <c r="S29" s="2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R29" s="2" t="inlineStr">
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2773,28 +3053,37 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N30" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q30" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O30" s="3" t="n">
+      <c r="R30" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P30" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q30" s="3" t="n">
+      <c r="S30" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T30" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R30" s="3" t="inlineStr">
+      <c r="U30" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2851,28 +3140,37 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N31" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="R31" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q31" s="3" t="n">
+      <c r="S31" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R31" s="3" t="inlineStr">
+      <c r="U31" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -2929,28 +3227,37 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N32" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O32" s="3" t="n">
+      <c r="R32" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P32" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+      <c r="S32" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="3" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -3007,28 +3314,37 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O33" s="3" t="n">
+      <c r="R33" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P33" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+      <c r="S33" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T33" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R33" s="3" t="inlineStr">
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -3085,28 +3401,37 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>15/0/0</t>
+          <t>24/3/2</t>
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>4.08</v>
+        <v>0.5</v>
       </c>
       <c r="N34" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>7.8</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="R34" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="P34" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+      <c r="S34" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R34" s="3" t="inlineStr">
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -3170,21 +3495,28 @@
         <v>0.005</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="R35" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="S35" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="T35" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R35" s="3" t="inlineStr">
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3248,21 +3580,28 @@
         <v>0.005</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="n"/>
+      <c r="P36" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="R36" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="S36" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="T36" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R36" s="3" t="inlineStr">
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3326,21 +3665,28 @@
         <v>0.005</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O37" s="3" t="n">
+      <c r="R37" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P37" s="3" t="n">
+      <c r="S37" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="T37" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R37" s="3" t="inlineStr">
+      <c r="U37" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3404,21 +3750,28 @@
         <v>0.005</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3" t="n"/>
+      <c r="P38" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q38" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="R38" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="S38" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="T38" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R38" s="3" t="inlineStr">
+      <c r="U38" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3482,21 +3835,28 @@
         <v>0.005</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="R39" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P39" s="3" t="n">
+      <c r="S39" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="T39" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R39" s="3" t="inlineStr">
+      <c r="U39" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3560,21 +3920,28 @@
         <v>0.005</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>3.98</v>
+        <v>0.2</v>
       </c>
       <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3" t="n"/>
+      <c r="P40" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="O40" s="3" t="n">
+      <c r="R40" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="P40" s="3" t="n">
+      <c r="S40" s="3" t="n">
         <v>2.61</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="T40" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="R40" s="3" t="inlineStr">
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -3631,28 +3998,37 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>166/41/31</t>
+          <t>180/41/31</t>
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.172</v>
+        <v>0.163</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>5.06</v>
+        <v>0.9</v>
       </c>
       <c r="N41" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>5.93</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="R41" s="3" t="n">
         <v>5.93</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="S41" s="3" t="n">
         <v>5.93</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="T41" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="R41" s="3" t="inlineStr">
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -3709,28 +4085,37 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>166/41/31</t>
+          <t>180/41/31</t>
         </is>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.172</v>
+        <v>0.163</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>5.06</v>
+        <v>0.9</v>
       </c>
       <c r="N42" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="Q42" s="4" t="n">
         <v>5.93</v>
       </c>
-      <c r="O42" s="4" t="n">
+      <c r="R42" s="4" t="n">
         <v>5.93</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="S42" s="4" t="n">
         <v>5.93</v>
       </c>
-      <c r="Q42" s="4" t="n">
+      <c r="T42" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="R42" s="4" t="inlineStr">
+      <c r="U42" s="4" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -3776,7 +4161,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3785,28 +4170,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>24/26/4</t>
+          <t>26/26/4</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0.481</v>
+        <v>0.464</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3.23</v>
+        <v>0.5</v>
       </c>
       <c r="N43" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q43" s="2" t="n">
         <v>7.51</v>
       </c>
-      <c r="O43" s="2" t="n">
+      <c r="R43" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="P43" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="Q43" s="2" t="n">
+      <c r="S43" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T43" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="U43" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -3861,28 +4255,37 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>24/26/4</t>
+          <t>26/26/4</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0.481</v>
+        <v>0.464</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3.23</v>
+        <v>0.5</v>
       </c>
       <c r="N44" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Q44" s="2" t="n">
         <v>7.51</v>
       </c>
-      <c r="O44" s="2" t="n">
+      <c r="R44" s="2" t="n">
         <v>7.52</v>
       </c>
-      <c r="P44" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="Q44" s="2" t="n">
+      <c r="S44" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T44" s="2" t="n">
         <v>0.95</v>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="U44" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -3939,28 +4342,37 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>11/26/0</t>
+          <t>16/30/0</t>
         </is>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.703</v>
+        <v>0.652</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>3.64</v>
+        <v>0.3</v>
       </c>
       <c r="N45" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Q45" s="3" t="n">
         <v>5.68</v>
       </c>
-      <c r="O45" s="3" t="n">
+      <c r="R45" s="3" t="n">
         <v>5.67</v>
       </c>
-      <c r="P45" s="3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Q45" s="3" t="n">
+      <c r="S45" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T45" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="R45" s="3" t="inlineStr">
+      <c r="U45" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4017,28 +4429,37 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>11/26/0</t>
+          <t>16/30/0</t>
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.703</v>
+        <v>0.652</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>3.64</v>
+        <v>0.3</v>
       </c>
       <c r="N46" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Q46" s="3" t="n">
         <v>5.68</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="R46" s="3" t="n">
         <v>5.67</v>
       </c>
-      <c r="P46" s="3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+      <c r="S46" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T46" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="R46" s="3" t="inlineStr">
+      <c r="U46" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4095,28 +4516,37 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>11/26/0</t>
+          <t>16/30/0</t>
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.703</v>
+        <v>0.652</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>3.64</v>
+        <v>0.3</v>
       </c>
       <c r="N47" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Q47" s="3" t="n">
         <v>5.68</v>
       </c>
-      <c r="O47" s="3" t="n">
+      <c r="R47" s="3" t="n">
         <v>5.67</v>
       </c>
-      <c r="P47" s="3" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Q47" s="3" t="n">
+      <c r="S47" s="3" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="T47" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="R47" s="3" t="inlineStr">
+      <c r="U47" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4173,28 +4603,37 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>77/22/2</t>
+          <t>88/30/2</t>
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.218</v>
+        <v>0.25</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.94</v>
+        <v>1.8</v>
       </c>
       <c r="N48" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="Q48" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="O48" s="3" t="n">
+      <c r="R48" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="P48" s="3" t="n">
+      <c r="S48" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q48" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
+      <c r="T48" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -4251,28 +4690,37 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>77/22/2</t>
+          <t>88/30/2</t>
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.218</v>
+        <v>0.25</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>8.94</v>
+        <v>1.8</v>
       </c>
       <c r="N49" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="Q49" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="O49" s="3" t="n">
+      <c r="R49" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="P49" s="3" t="n">
+      <c r="S49" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q49" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
+      <c r="T49" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -4318,7 +4766,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4327,28 +4775,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>140/58/16</t>
+          <t>146/66/16</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.271</v>
+        <v>0.289</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4.77</v>
+        <v>0.3</v>
       </c>
       <c r="N50" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q50" s="2" t="n">
         <v>5.97</v>
       </c>
-      <c r="O50" s="2" t="n">
+      <c r="R50" s="2" t="n">
         <v>5.97</v>
       </c>
-      <c r="P50" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4394,7 +4851,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4403,28 +4860,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>140/58/16</t>
+          <t>146/66/16</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.271</v>
+        <v>0.289</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4.77</v>
+        <v>0.3</v>
       </c>
       <c r="N51" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Q51" s="2" t="n">
         <v>5.97</v>
       </c>
-      <c r="O51" s="2" t="n">
+      <c r="R51" s="2" t="n">
         <v>5.97</v>
       </c>
-      <c r="P51" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="S51" s="2" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4470,7 +4936,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>427</v>
+        <v>495</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4479,28 +4945,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>27/46/0</t>
+          <t>33/48/0</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.63</v>
+        <v>0.593</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4.27</v>
+        <v>0.3</v>
       </c>
       <c r="N52" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="Q52" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="O52" s="2" t="n">
+      <c r="R52" s="2" t="n">
         <v>6.38</v>
       </c>
-      <c r="P52" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="Q52" s="2" t="n">
+      <c r="S52" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="T52" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="U52" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4555,28 +5030,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>27/46/0</t>
+          <t>33/48/0</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0.63</v>
+        <v>0.593</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4.27</v>
+        <v>0.3</v>
       </c>
       <c r="N53" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="Q53" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="O53" s="2" t="n">
+      <c r="R53" s="2" t="n">
         <v>6.38</v>
       </c>
-      <c r="P53" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="Q53" s="2" t="n">
+      <c r="S53" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="T53" s="2" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="U53" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -4633,28 +5117,37 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>13/0/0</t>
+          <t>18/2/0</t>
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>4.51</v>
+        <v>0.2</v>
       </c>
       <c r="N54" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="Q54" s="3" t="n">
         <v>6.42</v>
       </c>
-      <c r="O54" s="3" t="n">
+      <c r="R54" s="3" t="n">
         <v>5.39</v>
       </c>
-      <c r="P54" s="3" t="n">
+      <c r="S54" s="3" t="n">
         <v>6.42</v>
       </c>
-      <c r="Q54" s="3" t="n">
+      <c r="T54" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="R54" s="3" t="inlineStr">
+      <c r="U54" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -4716,21 +5209,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4.04</v>
+        <v>0.1</v>
       </c>
       <c r="N55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="Q55" s="2" t="n">
         <v>4.92</v>
       </c>
-      <c r="O55" s="2" t="n">
+      <c r="R55" s="2" t="n">
         <v>5.15</v>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="S55" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q55" s="2" t="n">
+      <c r="T55" s="2" t="n">
         <v>1.52</v>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="U55" s="2" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -4794,87 +5294,103 @@
         <v>0.503</v>
       </c>
       <c r="M56" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="N56" s="4" t="n"/>
-      <c r="O56" s="4" t="n"/>
-      <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
-      <c r="R56" s="4" t="inlineStr"/>
+      <c r="R56" s="4" t="n"/>
+      <c r="S56" s="4" t="n"/>
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="4" t="n">
         <v>236</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>DBS4-SP-Bamboo Twin Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-BURGUNDY-NEW</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>143443584538583</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>tos</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>DEAL, CEILINGED</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>0/6/0</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N57" s="3" t="n">
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>CLIMB-MIX-FIRST, DEAL, CEILINGED</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>1/23/0</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q57" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="O57" s="3" t="n">
+      <c r="R57" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="P57" s="3" t="n">
+      <c r="S57" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="Q57" s="3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
+      <c r="T57" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U57" s="4" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -4931,106 +5447,124 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>0/6/0</t>
+          <t>1/23/0</t>
         </is>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1</v>
+        <v>0.958</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N58" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q58" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="O58" s="4" t="n">
+      <c r="R58" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="P58" s="4" t="n">
+      <c r="S58" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="Q58" s="4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R58" s="4" t="inlineStr">
+      <c r="T58" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>DBS4-SP-Bamboo Twin Sheets-[Bamboo|Twin]-(LSV)-Exact-(Ranking)-DO-BAMBOO-TWIN-BURGUNDY-NEW</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>143443584538583</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>target · bamboo twin sheets</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>BASE-CUT-NO-DELIVERY, DEAL</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>0/6/0</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" s="3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N59" s="3" t="n">
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>DEAL</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>1/23/0</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q59" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="O59" s="3" t="n">
+      <c r="R59" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="P59" s="3" t="n">
+      <c r="S59" s="4" t="n">
         <v>3.53</v>
       </c>
-      <c r="Q59" s="3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
+      <c r="T59" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U59" s="4" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -5087,28 +5621,37 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>13/1/5</t>
+          <t>16/5/6</t>
         </is>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.053</v>
+        <v>0.185</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>4.36</v>
+        <v>0.1</v>
       </c>
       <c r="N60" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="Q60" s="4" t="n">
         <v>5.87</v>
       </c>
-      <c r="O60" s="4" t="n">
+      <c r="R60" s="4" t="n">
         <v>5.84</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="S60" s="4" t="n">
         <v>5.87</v>
       </c>
-      <c r="Q60" s="4" t="n">
+      <c r="T60" s="4" t="n">
         <v>2.92</v>
       </c>
-      <c r="R60" s="4" t="inlineStr">
+      <c r="U60" s="4" t="inlineStr">
         <is>
           <t>price held</t>
         </is>
@@ -5172,21 +5715,28 @@
         <v>0.551</v>
       </c>
       <c r="M61" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3" t="n"/>
+      <c r="P61" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="Q61" s="3" t="n">
         <v>2.55</v>
       </c>
-      <c r="O61" s="3" t="n">
+      <c r="R61" s="3" t="n">
         <v>2.55</v>
       </c>
-      <c r="P61" s="3" t="n">
+      <c r="S61" s="3" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q61" s="3" t="n">
+      <c r="T61" s="3" t="n">
         <v>0.95</v>
       </c>
-      <c r="R61" s="3" t="inlineStr">
+      <c r="U61" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -5232,37 +5782,46 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>PREMIUM-UNFUNDED, STOCK, PLACEMENT-READ, DEAL, CEILINGED</t>
+          <t>CLIMB-MIX-FIRST, PREMIUM-UNFUNDED, STOCK, PLACEMENT-READ, DEAL, CEILINGED</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0/1/0</t>
+          <t>1/15/1</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0.882</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q62" s="2" t="n">
         <v>5.32</v>
       </c>
-      <c r="O62" s="2" t="n">
+      <c r="R62" s="2" t="n">
         <v>5.91</v>
       </c>
-      <c r="P62" s="2" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
+      <c r="S62" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -5319,28 +5878,37 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>2/4/0</t>
+          <t>4/7/0</t>
         </is>
       </c>
       <c r="L63" s="3" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O63" s="3" t="n">
         <v>0.667</v>
       </c>
-      <c r="M63" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N63" s="3" t="n">
+      <c r="P63" s="3" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="Q63" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="O63" s="3" t="n">
+      <c r="R63" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="P63" s="3" t="n">
+      <c r="S63" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="Q63" s="3" t="n">
+      <c r="T63" s="3" t="n">
         <v>1.81</v>
       </c>
-      <c r="R63" s="3" t="inlineStr">
+      <c r="U63" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -5397,28 +5965,37 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>5/0/0</t>
+          <t>7/0/0</t>
         </is>
       </c>
       <c r="L64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>4.79</v>
+        <v>0.1</v>
       </c>
       <c r="N64" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q64" s="4" t="n">
         <v>4.94</v>
       </c>
-      <c r="O64" s="4" t="n">
+      <c r="R64" s="4" t="n">
         <v>5.18</v>
       </c>
-      <c r="P64" s="4" t="n">
+      <c r="S64" s="4" t="n">
         <v>5.18</v>
       </c>
-      <c r="Q64" s="4" t="n">
+      <c r="T64" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R64" s="4" t="inlineStr">
+      <c r="U64" s="4" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -5475,28 +6052,37 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>2/0/0</t>
+          <t>8/1/0</t>
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>4.53</v>
+        <v>0.1</v>
       </c>
       <c r="N65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q65" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="O65" s="3" t="n">
+      <c r="R65" s="3" t="n">
         <v>5.98</v>
       </c>
-      <c r="P65" s="3" t="n">
+      <c r="S65" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="Q65" s="3" t="n">
+      <c r="T65" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="R65" s="3" t="inlineStr">
+      <c r="U65" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -5553,28 +6139,37 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2/0/0</t>
+          <t>6/0/0</t>
         </is>
       </c>
       <c r="L66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>4.53</v>
+        <v>0.1</v>
       </c>
       <c r="N66" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q66" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="O66" s="3" t="n">
+      <c r="R66" s="3" t="n">
         <v>6.31</v>
       </c>
-      <c r="P66" s="3" t="n">
+      <c r="S66" s="3" t="n">
         <v>5.08</v>
       </c>
-      <c r="Q66" s="3" t="n">
+      <c r="T66" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R66" s="3" t="inlineStr">
+      <c r="U66" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -5631,28 +6226,37 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>3/0/1</t>
+          <t>5/0/1</t>
         </is>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>4.53</v>
+        <v>0.1</v>
       </c>
       <c r="N67" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q67" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="O67" s="3" t="n">
+      <c r="R67" s="3" t="n">
         <v>5.98</v>
       </c>
-      <c r="P67" s="3" t="n">
+      <c r="S67" s="3" t="n">
         <v>4.79</v>
       </c>
-      <c r="Q67" s="3" t="n">
+      <c r="T67" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="R67" s="3" t="inlineStr">
+      <c r="U67" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -5709,28 +6313,37 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>72/17/15</t>
+          <t>72/18/15</t>
         </is>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.163</v>
+        <v>0.171</v>
       </c>
       <c r="M68" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="3" t="n">
         <v>5.27</v>
       </c>
-      <c r="N68" s="3" t="n">
+      <c r="Q68" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="O68" s="3" t="n">
+      <c r="R68" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="P68" s="3" t="n">
+      <c r="S68" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q68" s="3" t="n">
+      <c r="T68" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R68" s="3" t="inlineStr">
+      <c r="U68" s="3" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -5792,21 +6405,28 @@
         <v>0.796</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="Q69" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="O69" s="2" t="n">
+      <c r="R69" s="2" t="n">
         <v>4.72</v>
       </c>
-      <c r="P69" s="2" t="n">
+      <c r="S69" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q69" s="2" t="n">
+      <c r="T69" s="2" t="n">
         <v>1.07</v>
       </c>
-      <c r="R69" s="2" t="inlineStr">
+      <c r="U69" s="2" t="inlineStr">
         <is>
           <t>price held</t>
         </is>
@@ -5863,28 +6483,37 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>12/16/1</t>
+          <t>19/17/1</t>
         </is>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.552</v>
+        <v>0.459</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>4.27</v>
+        <v>0.2</v>
       </c>
       <c r="N70" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="Q70" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="O70" s="3" t="n">
+      <c r="R70" s="3" t="n">
         <v>2.37</v>
       </c>
-      <c r="P70" s="3" t="n">
+      <c r="S70" s="3" t="n">
         <v>2.41</v>
       </c>
-      <c r="Q70" s="3" t="n">
+      <c r="T70" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="R70" s="3" t="inlineStr">
+      <c r="U70" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -5939,28 +6568,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2/5/11</t>
+          <t>2/6/12</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q71" s="2" t="n">
         <v>3.72</v>
       </c>
-      <c r="O71" s="2" t="n">
+      <c r="R71" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="S71" s="2" t="n">
         <v>3.72</v>
       </c>
-      <c r="Q71" s="2" t="n">
+      <c r="T71" s="2" t="n">
         <v>1.14</v>
       </c>
-      <c r="R71" s="2" t="inlineStr">
+      <c r="U71" s="2" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -6015,28 +6653,37 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2/5/11</t>
+          <t>2/6/12</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="Q72" s="2" t="n">
         <v>3.72</v>
       </c>
-      <c r="O72" s="2" t="n">
+      <c r="R72" s="2" t="n">
         <v>3.35</v>
       </c>
-      <c r="P72" s="2" t="n">
+      <c r="S72" s="2" t="n">
         <v>3.72</v>
       </c>
-      <c r="Q72" s="2" t="n">
+      <c r="T72" s="2" t="n">
         <v>1.14</v>
       </c>
-      <c r="R72" s="2" t="inlineStr">
+      <c r="U72" s="2" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -6093,28 +6740,37 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>1/14/0</t>
+          <t>1/18/0</t>
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="Q73" s="3" t="n">
         <v>6.42</v>
       </c>
-      <c r="O73" s="3" t="n">
+      <c r="R73" s="3" t="n">
         <v>7.12</v>
       </c>
-      <c r="P73" s="3" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="Q73" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R73" s="3" t="inlineStr">
+      <c r="S73" s="3" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U73" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -6160,7 +6816,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6169,28 +6825,37 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0/4/0</t>
+          <t>0/6/0</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="Q74" s="2" t="n">
         <v>5.8</v>
       </c>
-      <c r="O74" s="2" t="n">
+      <c r="R74" s="2" t="n">
         <v>6.41</v>
       </c>
-      <c r="P74" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="Q74" s="2" t="n">
+      <c r="S74" s="2" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="T74" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="U74" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -6236,7 +6901,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6252,21 +6917,28 @@
         <v>0</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4.36</v>
+        <v>0.1</v>
       </c>
       <c r="N75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2" t="n"/>
+      <c r="P75" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q75" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="O75" s="2" t="n">
+      <c r="R75" s="2" t="n">
         <v>5.07</v>
       </c>
-      <c r="P75" s="2" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q75" s="2" t="n">
+      <c r="S75" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T75" s="2" t="n">
         <v>1.6</v>
       </c>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="U75" s="2" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -6321,28 +6993,37 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>11/42/3</t>
+          <t>11/45/3</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0.75</v>
+        <v>0.763</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="N76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Q76" s="2" t="n">
         <v>4.99</v>
       </c>
-      <c r="O76" s="2" t="n">
+      <c r="R76" s="2" t="n">
         <v>6.32</v>
       </c>
-      <c r="P76" s="2" t="n">
+      <c r="S76" s="2" t="n">
         <v>4.99</v>
       </c>
-      <c r="Q76" s="2" t="n">
+      <c r="T76" s="2" t="n">
         <v>1.69</v>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="U76" s="2" t="inlineStr">
         <is>
           <t>price held at ceiling</t>
         </is>
@@ -6388,7 +7069,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6397,28 +7078,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3/0/0</t>
+          <t>4/0/0</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4.96</v>
+        <v>0.1</v>
       </c>
       <c r="N77" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Q77" s="2" t="n">
         <v>4.41</v>
       </c>
-      <c r="O77" s="2" t="n">
+      <c r="R77" s="2" t="n">
         <v>5.52</v>
       </c>
-      <c r="P77" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="Q77" s="2" t="n">
+      <c r="S77" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T77" s="2" t="n">
         <v>1.32</v>
       </c>
-      <c r="R77" s="2" t="inlineStr">
+      <c r="U77" s="2" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -6473,28 +7163,37 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>4/0/0</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q78" s="2" t="n">
         <v>4.79</v>
       </c>
-      <c r="O78" s="2" t="n">
+      <c r="R78" s="2" t="n">
         <v>5.98</v>
       </c>
-      <c r="P78" s="2" t="n">
+      <c r="S78" s="2" t="n">
         <v>6.23</v>
       </c>
-      <c r="Q78" s="2" t="n">
+      <c r="T78" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="R78" s="2" t="inlineStr">
+      <c r="U78" s="2" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -6551,28 +7250,37 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>5/4/1</t>
+          <t>7/4/1</t>
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N79" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q79" s="3" t="n">
         <v>5.32</v>
       </c>
-      <c r="O79" s="3" t="n">
+      <c r="R79" s="3" t="n">
         <v>6.47</v>
       </c>
-      <c r="P79" s="3" t="n">
+      <c r="S79" s="3" t="n">
         <v>5.32</v>
       </c>
-      <c r="Q79" s="3" t="n">
+      <c r="T79" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="R79" s="3" t="inlineStr">
+      <c r="U79" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -6629,28 +7337,37 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>7/0/0</t>
+          <t>8/0/0</t>
         </is>
       </c>
       <c r="L80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N80" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q80" s="3" t="n">
         <v>6.17</v>
       </c>
-      <c r="O80" s="3" t="n">
+      <c r="R80" s="3" t="n">
         <v>6.48</v>
       </c>
-      <c r="P80" s="3" t="n">
+      <c r="S80" s="3" t="n">
         <v>6.17</v>
       </c>
-      <c r="Q80" s="3" t="n">
+      <c r="T80" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R80" s="3" t="inlineStr">
+      <c r="U80" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -6705,28 +7422,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>3/0/0</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N81" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q81" s="2" t="n">
         <v>4.79</v>
       </c>
-      <c r="O81" s="2" t="n">
+      <c r="R81" s="2" t="n">
         <v>5.98</v>
       </c>
-      <c r="P81" s="2" t="n">
+      <c r="S81" s="2" t="n">
         <v>6.23</v>
       </c>
-      <c r="Q81" s="2" t="n">
+      <c r="T81" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="R81" s="2" t="inlineStr">
+      <c r="U81" s="2" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -6783,28 +7509,37 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>9/0/0</t>
+          <t>11/0/0</t>
         </is>
       </c>
       <c r="L82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N82" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q82" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="O82" s="3" t="n">
+      <c r="R82" s="3" t="n">
         <v>6.48</v>
       </c>
-      <c r="P82" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q82" s="3" t="n">
+      <c r="S82" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T82" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R82" s="3" t="inlineStr">
+      <c r="U82" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -6861,30 +7596,39 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>0/1/0</t>
+          <t>1/3/0</t>
         </is>
       </c>
       <c r="L83" s="3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q83" s="3" t="n">
         <v>6.84</v>
       </c>
-      <c r="O83" s="3" t="n">
+      <c r="R83" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="P83" s="3" t="n">
+      <c r="S83" s="3" t="n">
         <v>6.84</v>
       </c>
-      <c r="Q83" s="3" t="n">
+      <c r="T83" s="3" t="n">
         <v>2.78</v>
       </c>
-      <c r="R83" s="3" t="inlineStr">
-        <is>
-          <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
+      <c r="U83" s="3" t="inlineStr">
+        <is>
+          <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
       </c>
     </row>
@@ -6939,28 +7683,37 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2/0/0</t>
+          <t>3/0/0</t>
         </is>
       </c>
       <c r="L84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>4.53</v>
+        <v>0.1</v>
       </c>
       <c r="N84" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q84" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="O84" s="3" t="n">
+      <c r="R84" s="3" t="n">
         <v>6.37</v>
       </c>
-      <c r="P84" s="3" t="n">
+      <c r="S84" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="Q84" s="3" t="n">
+      <c r="T84" s="3" t="n">
         <v>1.57</v>
       </c>
-      <c r="R84" s="3" t="inlineStr">
+      <c r="U84" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -7017,28 +7770,37 @@
       </c>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>2/0/1</t>
+          <t>3/0/1</t>
         </is>
       </c>
       <c r="L85" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N85" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Q85" s="4" t="n">
         <v>7.76</v>
       </c>
-      <c r="O85" s="4" t="n">
+      <c r="R85" s="4" t="n">
         <v>7.76</v>
       </c>
-      <c r="P85" s="4" t="n">
+      <c r="S85" s="4" t="n">
         <v>10.09</v>
       </c>
-      <c r="Q85" s="4" t="n">
+      <c r="T85" s="4" t="n">
         <v>2.44</v>
       </c>
-      <c r="R85" s="4" t="inlineStr">
+      <c r="U85" s="4" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -7100,21 +7862,28 @@
         <v>0.439</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="N86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2" t="n"/>
+      <c r="P86" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Q86" s="2" t="n">
         <v>4.71</v>
       </c>
-      <c r="O86" s="2" t="n">
+      <c r="R86" s="2" t="n">
         <v>5.9</v>
       </c>
-      <c r="P86" s="2" t="n">
+      <c r="S86" s="2" t="n">
         <v>6.13</v>
       </c>
-      <c r="Q86" s="2" t="n">
+      <c r="T86" s="2" t="n">
         <v>0.86</v>
       </c>
-      <c r="R86" s="2" t="inlineStr">
+      <c r="U86" s="2" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -7178,21 +7947,28 @@
         <v>0.333</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3" t="n"/>
+      <c r="P87" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Q87" s="3" t="n">
         <v>4.52</v>
       </c>
-      <c r="O87" s="3" t="n">
+      <c r="R87" s="3" t="n">
         <v>5.64</v>
       </c>
-      <c r="P87" s="3" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q87" s="3" t="n">
+      <c r="S87" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T87" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R87" s="3" t="inlineStr">
+      <c r="U87" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -7249,104 +8025,124 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L88" s="4" t="n"/>
+          <t>0/1/2</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="n">
+        <v>0.333</v>
+      </c>
       <c r="M88" s="4" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q88" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="O88" s="4" t="n">
+      <c r="R88" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="P88" s="4" t="n">
+      <c r="S88" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="Q88" s="4" t="n">
+      <c r="T88" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R88" s="4" t="inlineStr">
+      <c r="U88" s="4" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="2" t="n">
         <v>685</v>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>DBS4-SP-Bamboo Bedsheets-[Bamboo]-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>546212532391520</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>tos</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>303</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>PUSH-UNPROVEN, PLACEMENT-READ, DEAL, PREDICTION</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N89" s="3" t="n">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>PLACEMENT-READ, DEAL, PREDICTION</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>2/0/0</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q89" s="2" t="n">
         <v>5.1</v>
       </c>
-      <c r="O89" s="3" t="n">
+      <c r="R89" s="2" t="n">
         <v>6.33</v>
       </c>
-      <c r="P89" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Q89" s="3" t="n">
+      <c r="S89" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="T89" s="2" t="n">
         <v>1.57</v>
       </c>
-      <c r="R89" s="3" t="inlineStr">
-        <is>
-          <t>price held above the ceiling — the premium is not a proven push (CTR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>funding step (≤ +30%)</t>
         </is>
       </c>
     </row>
@@ -7401,30 +8197,39 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>0/0/1</t>
+          <t>1/0/1</t>
         </is>
       </c>
       <c r="L90" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N90" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q90" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="O90" s="4" t="n">
+      <c r="R90" s="4" t="n">
         <v>4.16</v>
       </c>
-      <c r="P90" s="4" t="n">
+      <c r="S90" s="4" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q90" s="4" t="n">
+      <c r="T90" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="R90" s="4" t="inlineStr">
-        <is>
-          <t>climb toward the ceiling only (≤ +30%) — no premium until CTR above market shown</t>
+      <c r="U90" s="4" t="inlineStr">
+        <is>
+          <t>funding step (≤ +30%)</t>
         </is>
       </c>
     </row>
@@ -7479,26 +8284,37 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L91" s="3" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M91" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q91" s="3" t="n">
         <v>4.73</v>
       </c>
-      <c r="O91" s="3" t="n">
+      <c r="R91" s="3" t="n">
         <v>5.92</v>
       </c>
-      <c r="P91" s="3" t="n">
+      <c r="S91" s="3" t="n">
         <v>4.73</v>
       </c>
-      <c r="Q91" s="3" t="n">
+      <c r="T91" s="3" t="n">
         <v>1.45</v>
       </c>
-      <c r="R91" s="3" t="inlineStr">
+      <c r="U91" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -7555,28 +8371,37 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>2/7/0</t>
+          <t>4/7/0</t>
         </is>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.778</v>
+        <v>0.636</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N92" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q92" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="O92" s="4" t="n">
+      <c r="R92" s="4" t="n">
         <v>4.15</v>
       </c>
-      <c r="P92" s="4" t="n">
+      <c r="S92" s="4" t="n">
         <v>4.15</v>
       </c>
-      <c r="Q92" s="4" t="n">
+      <c r="T92" s="4" t="n">
         <v>1.36</v>
       </c>
-      <c r="R92" s="4" t="inlineStr">
+      <c r="U92" s="4" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -7622,11 +8447,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>STOCK, PLACEMENT-READ</t>
+          <t>PREMIUM-UNFUNDED, STOCK, PLACEMENT-READ</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7638,21 +8463,28 @@
         <v>0.538</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="N93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="2" t="n"/>
+      <c r="P93" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Q93" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O93" s="2" t="n">
+      <c r="R93" s="2" t="n">
         <v>4.99</v>
       </c>
-      <c r="P93" s="2" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="Q93" s="2" t="n">
+      <c r="S93" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T93" s="2" t="n">
         <v>1.28</v>
       </c>
-      <c r="R93" s="2" t="inlineStr">
+      <c r="U93" s="2" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -7716,21 +8548,28 @@
         <v>0</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q94" s="3" t="n">
         <v>5.78</v>
       </c>
-      <c r="O94" s="3" t="n">
+      <c r="R94" s="3" t="n">
         <v>6.47</v>
       </c>
-      <c r="P94" s="3" t="n">
+      <c r="S94" s="3" t="n">
         <v>5.78</v>
       </c>
-      <c r="Q94" s="3" t="n">
+      <c r="T94" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R94" s="3" t="inlineStr">
+      <c r="U94" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -7794,93 +8633,109 @@
         <v>0.167</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>4.09</v>
+        <v>0.1</v>
       </c>
       <c r="N95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="Q95" s="3" t="n">
         <v>4.52</v>
       </c>
-      <c r="O95" s="3" t="n">
+      <c r="R95" s="3" t="n">
         <v>5.64</v>
       </c>
-      <c r="P95" s="3" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="Q95" s="3" t="n">
+      <c r="S95" s="3" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T95" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R95" s="3" t="inlineStr">
+      <c r="U95" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="4" t="n">
         <v>776</v>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>DBS4-SP-King Bamboo Sheets Deep Pocket-(LSV)-Exact-(Ranking)-DO-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>339900598915705</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>tos</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr"/>
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>1/0/0</t>
         </is>
       </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N96" s="2" t="n">
+      <c r="L96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="4" t="n"/>
+      <c r="P96" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q96" s="4" t="n">
         <v>3.58</v>
       </c>
-      <c r="O96" s="2" t="n">
+      <c r="R96" s="4" t="n">
         <v>4.47</v>
       </c>
-      <c r="P96" s="2" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q96" s="2" t="n">
+      <c r="S96" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T96" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="R96" s="2" t="inlineStr">
+      <c r="U96" s="4" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -7926,7 +8781,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7935,28 +8790,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M97" s="2" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N97" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q97" s="2" t="n">
         <v>3.51</v>
       </c>
-      <c r="O97" s="2" t="n">
+      <c r="R97" s="2" t="n">
         <v>4.39</v>
       </c>
-      <c r="P97" s="2" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q97" s="2" t="n">
+      <c r="S97" s="2" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="T97" s="2" t="n">
         <v>1.3</v>
       </c>
-      <c r="R97" s="2" t="inlineStr">
-        <is>
-          <t>climb toward the ceiling only (≤ +30%) — no premium until CTR above market shown</t>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>funding step (≤ +30%)</t>
         </is>
       </c>
     </row>
@@ -8018,21 +8884,28 @@
         <v>0.079</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>3.82</v>
+        <v>0.1</v>
       </c>
       <c r="N98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3" t="n"/>
+      <c r="P98" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Q98" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="O98" s="3" t="n">
+      <c r="R98" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="P98" s="3" t="n">
+      <c r="S98" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="Q98" s="3" t="n">
+      <c r="T98" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R98" s="3" t="inlineStr">
+      <c r="U98" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -8078,7 +8951,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -8094,21 +8967,28 @@
         <v>0.375</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="2" t="n"/>
+      <c r="P99" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q99" s="2" t="n">
         <v>3.57</v>
       </c>
-      <c r="O99" s="2" t="n">
+      <c r="R99" s="2" t="n">
         <v>4.64</v>
       </c>
-      <c r="P99" s="2" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q99" s="2" t="n">
+      <c r="S99" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T99" s="2" t="n">
         <v>1.42</v>
       </c>
-      <c r="R99" s="2" t="inlineStr">
+      <c r="U99" s="2" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -8172,21 +9052,28 @@
         <v>0.2</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q100" s="3" t="n">
         <v>4.75</v>
       </c>
-      <c r="O100" s="3" t="n">
+      <c r="R100" s="3" t="n">
         <v>5.95</v>
       </c>
-      <c r="P100" s="3" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="Q100" s="3" t="n">
+      <c r="S100" s="3" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="T100" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R100" s="3" t="inlineStr">
+      <c r="U100" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -8232,7 +9119,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8241,28 +9128,37 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>2/0/0</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N101" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q101" s="2" t="n">
         <v>3.53</v>
       </c>
-      <c r="O101" s="2" t="n">
+      <c r="R101" s="2" t="n">
         <v>4.42</v>
       </c>
-      <c r="P101" s="2" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q101" s="2" t="n">
+      <c r="S101" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T101" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="R101" s="2" t="inlineStr">
+      <c r="U101" s="2" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded shown</t>
         </is>
@@ -8326,21 +9222,28 @@
         <v>0.545</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="n"/>
+      <c r="P102" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="Q102" s="3" t="n">
         <v>5.43</v>
       </c>
-      <c r="O102" s="3" t="n">
+      <c r="R102" s="3" t="n">
         <v>6.38</v>
       </c>
-      <c r="P102" s="3" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="Q102" s="3" t="n">
+      <c r="S102" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="T102" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="R102" s="3" t="inlineStr">
+      <c r="U102" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -8404,21 +9307,28 @@
         <v>0</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="3" t="n"/>
+      <c r="P103" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q103" s="3" t="n">
         <v>5.88</v>
       </c>
-      <c r="O103" s="3" t="n">
+      <c r="R103" s="3" t="n">
         <v>6.32</v>
       </c>
-      <c r="P103" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q103" s="3" t="n">
+      <c r="S103" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T103" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R103" s="3" t="inlineStr">
+      <c r="U103" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -8482,21 +9392,28 @@
         <v>0</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="N104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="3" t="n"/>
+      <c r="P104" s="3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q104" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="O104" s="3" t="n">
+      <c r="R104" s="3" t="n">
         <v>1.97</v>
       </c>
-      <c r="P104" s="3" t="n">
+      <c r="S104" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q104" s="3" t="n">
+      <c r="T104" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="R104" s="3" t="inlineStr">
+      <c r="U104" s="3" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until CTR above market shown</t>
         </is>
@@ -8560,21 +9477,28 @@
         <v>0.769</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="N105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="3" t="n"/>
+      <c r="P105" s="3" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Q105" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="O105" s="3" t="n">
+      <c r="R105" s="3" t="n">
         <v>3.62</v>
       </c>
-      <c r="P105" s="3" t="n">
+      <c r="S105" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="Q105" s="3" t="n">
+      <c r="T105" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="R105" s="3" t="inlineStr">
+      <c r="U105" s="3" t="inlineStr">
         <is>
           <t>price held under its ceiling (out of focus: the operator's taper releases this spend; the document would allow up to the ceiling)</t>
         </is>
@@ -8636,21 +9560,30 @@
         <v>0.5</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="N106" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="Q106" s="2" t="n">
         <v>4.87</v>
       </c>
-      <c r="O106" s="2" t="n">
+      <c r="R106" s="2" t="n">
         <v>6.08</v>
       </c>
-      <c r="P106" s="2" t="n">
+      <c r="S106" s="2" t="n">
         <v>4.87</v>
       </c>
-      <c r="Q106" s="2" t="n">
+      <c r="T106" s="2" t="n">
         <v>1.08</v>
       </c>
-      <c r="R106" s="2" t="inlineStr">
+      <c r="U106" s="2" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -8714,21 +9647,28 @@
         <v>0</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="3" t="n"/>
+      <c r="P107" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q107" s="3" t="n">
         <v>4.04</v>
       </c>
-      <c r="O107" s="3" t="n">
+      <c r="R107" s="3" t="n">
         <v>5.04</v>
       </c>
-      <c r="P107" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q107" s="3" t="n">
+      <c r="S107" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T107" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="R107" s="3" t="inlineStr">
+      <c r="U107" s="3" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -8792,21 +9732,28 @@
         <v>0</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="3" t="n"/>
+      <c r="P108" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q108" s="3" t="n">
         <v>4.94</v>
       </c>
-      <c r="O108" s="3" t="n">
+      <c r="R108" s="3" t="n">
         <v>5.18</v>
       </c>
-      <c r="P108" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q108" s="3" t="n">
+      <c r="S108" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T108" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R108" s="3" t="inlineStr">
+      <c r="U108" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling</t>
         </is>
@@ -8868,21 +9815,28 @@
       </c>
       <c r="L109" s="3" t="n"/>
       <c r="M109" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="O109" s="3" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O109" s="3" t="n"/>
       <c r="P109" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="Q109" s="3" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R109" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S109" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T109" s="3" t="n">
         <v>1.82</v>
       </c>
-      <c r="R109" s="3" t="inlineStr">
+      <c r="U109" s="3" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -8946,21 +9900,28 @@
         <v>0.059</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="3" t="n"/>
+      <c r="P110" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q110" s="3" t="n">
         <v>4.46</v>
       </c>
-      <c r="O110" s="3" t="n">
+      <c r="R110" s="3" t="n">
         <v>5.59</v>
       </c>
-      <c r="P110" s="3" t="n">
+      <c r="S110" s="3" t="n">
         <v>4.46</v>
       </c>
-      <c r="Q110" s="3" t="n">
+      <c r="T110" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R110" s="3" t="inlineStr">
+      <c r="U110" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -9024,13 +9985,20 @@
         <v>0</v>
       </c>
       <c r="M111" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N111" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N111" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O111" s="4" t="n"/>
-      <c r="P111" s="4" t="n"/>
+      <c r="P111" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q111" s="4" t="n"/>
-      <c r="R111" s="4" t="inlineStr"/>
+      <c r="R111" s="4" t="n"/>
+      <c r="S111" s="4" t="n"/>
+      <c r="T111" s="4" t="n"/>
+      <c r="U111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
@@ -9090,21 +10058,28 @@
         <v>0.25</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>4.36</v>
+        <v>0.2</v>
       </c>
       <c r="N112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3" t="n"/>
+      <c r="P112" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q112" s="3" t="n">
         <v>4.69</v>
       </c>
-      <c r="O112" s="3" t="n">
+      <c r="R112" s="3" t="n">
         <v>5.17</v>
       </c>
-      <c r="P112" s="3" t="n">
+      <c r="S112" s="3" t="n">
         <v>4.69</v>
       </c>
-      <c r="Q112" s="3" t="n">
+      <c r="T112" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R112" s="3" t="inlineStr">
+      <c r="U112" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -9168,21 +10143,28 @@
         <v>0</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3" t="n"/>
+      <c r="P113" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q113" s="3" t="n">
         <v>3.32</v>
       </c>
-      <c r="O113" s="3" t="n">
+      <c r="R113" s="3" t="n">
         <v>4.16</v>
       </c>
-      <c r="P113" s="3" t="n">
+      <c r="S113" s="3" t="n">
         <v>4.32</v>
       </c>
-      <c r="Q113" s="3" t="n">
+      <c r="T113" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R113" s="3" t="inlineStr">
+      <c r="U113" s="3" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -9228,7 +10210,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -9242,21 +10224,28 @@
       </c>
       <c r="L114" s="2" t="n"/>
       <c r="M114" s="2" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q114" s="2" t="n">
         <v>3.71</v>
       </c>
-      <c r="O114" s="2" t="n">
+      <c r="R114" s="2" t="n">
         <v>4.8</v>
       </c>
-      <c r="P114" s="2" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="Q114" s="2" t="n">
+      <c r="S114" s="2" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T114" s="2" t="n">
         <v>1.92</v>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="U114" s="2" t="inlineStr">
         <is>
           <t>climb toward the ceiling only (≤ +30%) — no premium until funded, CTR above market, CVR above market shown</t>
         </is>
@@ -9313,28 +10302,37 @@
       </c>
       <c r="K115" s="4" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>2/0/0</t>
         </is>
       </c>
       <c r="L115" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="4" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="N115" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q115" s="4" t="n">
         <v>6.29</v>
       </c>
-      <c r="O115" s="4" t="n">
+      <c r="R115" s="4" t="n">
         <v>6.38</v>
       </c>
-      <c r="P115" s="4" t="n">
+      <c r="S115" s="4" t="n">
         <v>6.39</v>
       </c>
-      <c r="Q115" s="4" t="n">
+      <c r="T115" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="R115" s="4" t="inlineStr">
+      <c r="U115" s="4" t="inlineStr">
         <is>
           <t>funding step (≤ +30%)</t>
         </is>
@@ -9396,21 +10394,28 @@
       </c>
       <c r="L116" s="3" t="n"/>
       <c r="M116" s="3" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="3" t="n"/>
+      <c r="P116" s="3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q116" s="3" t="n">
         <v>5.07</v>
       </c>
-      <c r="O116" s="3" t="n">
+      <c r="R116" s="3" t="n">
         <v>6.33</v>
       </c>
-      <c r="P116" s="3" t="n">
+      <c r="S116" s="3" t="n">
         <v>5.07</v>
       </c>
-      <c r="Q116" s="3" t="n">
+      <c r="T116" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="R116" s="3" t="inlineStr">
+      <c r="U116" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CTR above market, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -9474,21 +10479,28 @@
         <v>0.167</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="3" t="n"/>
+      <c r="P117" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q117" s="3" t="n">
         <v>2.96</v>
       </c>
-      <c r="O117" s="3" t="n">
+      <c r="R117" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="P117" s="3" t="n">
+      <c r="S117" s="3" t="n">
         <v>3.85</v>
       </c>
-      <c r="Q117" s="3" t="n">
+      <c r="T117" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R117" s="3" t="inlineStr">
+      <c r="U117" s="3" t="inlineStr">
         <is>
           <t>maintenance climb toward ceiling (≤ +30%)</t>
         </is>
@@ -9552,21 +10564,28 @@
         <v>0.333</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="3" t="n"/>
+      <c r="P118" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Q118" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="O118" s="3" t="n">
+      <c r="R118" s="3" t="n">
         <v>5.83</v>
       </c>
-      <c r="P118" s="3" t="n">
+      <c r="S118" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="Q118" s="3" t="n">
+      <c r="T118" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R118" s="3" t="inlineStr">
+      <c r="U118" s="3" t="inlineStr">
         <is>
           <t>price held above the ceiling — the premium is not a proven push (funded, CVR above market not shown); operator decision owed: prove/fund it or descend to the ceiling</t>
         </is>
@@ -9626,13 +10645,20 @@
         <v>0</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N119" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N119" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O119" s="5" t="n"/>
-      <c r="P119" s="5" t="n"/>
+      <c r="P119" s="5" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q119" s="5" t="n"/>
-      <c r="R119" s="5" t="inlineStr"/>
+      <c r="R119" s="5" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="5" t="n"/>
+      <c r="U119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -9688,13 +10714,20 @@
         <v>0</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N120" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N120" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O120" s="5" t="n"/>
-      <c r="P120" s="5" t="n"/>
+      <c r="P120" s="5" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q120" s="5" t="n"/>
-      <c r="R120" s="5" t="inlineStr"/>
+      <c r="R120" s="5" t="n"/>
+      <c r="S120" s="5" t="n"/>
+      <c r="T120" s="5" t="n"/>
+      <c r="U120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -9750,87 +10783,101 @@
         <v>0.081</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="N121" s="5" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="N121" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="O121" s="5" t="n"/>
-      <c r="P121" s="5" t="n"/>
+      <c r="P121" s="5" t="n">
+        <v>4.92</v>
+      </c>
       <c r="Q121" s="5" t="n"/>
-      <c r="R121" s="5" t="inlineStr"/>
+      <c r="R121" s="5" t="n"/>
+      <c r="S121" s="5" t="n"/>
+      <c r="T121" s="5" t="n"/>
+      <c r="U121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="2" t="n">
         <v>2160</v>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>DBS4-SP-Extra Deep 20-24 Inch Pocket King Size Bamboo Sheets-[Bamboo|King]-(LSV)-Exact-(Conversion)-FIX-BAMBOO-KING-WHITE</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>72421457858760</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>target · extra deep 20-24 inch pocket king size bamboo sheets</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>5/7/0</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="M122" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N122" s="3" t="n">
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>7/28/0</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q122" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="O122" s="3" t="n">
+      <c r="R122" s="2" t="n">
         <v>3.09</v>
       </c>
-      <c r="P122" s="3" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q122" s="3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R122" s="3" t="inlineStr">
+      <c r="S122" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U122" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -9883,106 +10930,122 @@
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>5/7/0</t>
+          <t>7/28/0</t>
         </is>
       </c>
       <c r="L123" s="5" t="n">
-        <v>0.583</v>
+        <v>0.8</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>4.53</v>
+        <v>0.2</v>
       </c>
       <c r="N123" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O123" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P123" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q123" s="5" t="n">
         <v>4.95</v>
       </c>
-      <c r="O123" s="5" t="n">
+      <c r="R123" s="5" t="n">
         <v>3.09</v>
       </c>
-      <c r="P123" s="5" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q123" s="5" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R123" s="5" t="inlineStr">
+      <c r="S123" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T123" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U123" s="5" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="2" t="n">
         <v>2162</v>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>DBS4-SP-bamboo sheets california king-[Bamboo|California King]-(LSV)-Broad-(DISC)-DO-BAMBOO-CALIFKING-WHITE</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>87932013445748</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>target · bamboo sheets california king</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>2.07</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>STOCK, DEAL</t>
         </is>
       </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>3/7/8</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="M124" s="3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N124" s="3" t="n">
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>6/10/32</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="Q124" s="2" t="n">
         <v>2.07</v>
       </c>
-      <c r="O124" s="3" t="n">
+      <c r="R124" s="2" t="n">
         <v>1.86</v>
       </c>
-      <c r="P124" s="3" t="n">
+      <c r="S124" s="2" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q124" s="3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R124" s="3" t="inlineStr">
+      <c r="T124" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U124" s="2" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -10035,28 +11098,37 @@
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>3/7/8</t>
+          <t>6/10/32</t>
         </is>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.389</v>
+        <v>0.208</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>4.75</v>
+        <v>0.1</v>
       </c>
       <c r="N125" s="5" t="n">
-        <v>2.07</v>
+        <v>0.5</v>
       </c>
       <c r="O125" s="5" t="n">
-        <v>1.86</v>
+        <v>0.132</v>
       </c>
       <c r="P125" s="5" t="n">
-        <v>2.07</v>
+        <v>4.47</v>
       </c>
       <c r="Q125" s="5" t="n">
         <v>2.07</v>
       </c>
-      <c r="R125" s="5" t="inlineStr">
+      <c r="R125" s="5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S125" s="5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T125" s="5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U125" s="5" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -10113,28 +11185,37 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N126" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P126" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q126" s="3" t="n">
         <v>5.43</v>
       </c>
-      <c r="O126" s="3" t="n">
+      <c r="R126" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="P126" s="3" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q126" s="3" t="n">
+      <c r="S126" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T126" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R126" s="3" t="inlineStr">
+      <c r="U126" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -10191,28 +11272,37 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N127" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O127" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P127" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q127" s="3" t="n">
         <v>5.43</v>
       </c>
-      <c r="O127" s="3" t="n">
+      <c r="R127" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="P127" s="3" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q127" s="3" t="n">
+      <c r="S127" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T127" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R127" s="3" t="inlineStr">
+      <c r="U127" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -10269,28 +11359,37 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L128" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N128" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P128" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q128" s="3" t="n">
         <v>5.43</v>
       </c>
-      <c r="O128" s="3" t="n">
+      <c r="R128" s="3" t="n">
         <v>3.67</v>
       </c>
-      <c r="P128" s="3" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q128" s="3" t="n">
+      <c r="S128" s="3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T128" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R128" s="3" t="inlineStr">
+      <c r="U128" s="3" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -10343,28 +11442,37 @@
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N129" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O129" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P129" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q129" s="5" t="n">
         <v>5.43</v>
       </c>
-      <c r="O129" s="5" t="n">
+      <c r="R129" s="5" t="n">
         <v>3.67</v>
       </c>
-      <c r="P129" s="5" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q129" s="5" t="n">
+      <c r="S129" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T129" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="R129" s="5" t="inlineStr">
+      <c r="U129" s="5" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -10417,28 +11525,37 @@
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L130" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N130" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O130" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P130" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q130" s="5" t="n">
         <v>5.43</v>
       </c>
-      <c r="O130" s="5" t="n">
+      <c r="R130" s="5" t="n">
         <v>3.67</v>
       </c>
-      <c r="P130" s="5" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q130" s="5" t="n">
+      <c r="S130" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T130" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="R130" s="5" t="inlineStr">
+      <c r="U130" s="5" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -10491,560 +11608,646 @@
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L131" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N131" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O131" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P131" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q131" s="5" t="n">
         <v>5.43</v>
       </c>
-      <c r="O131" s="5" t="n">
+      <c r="R131" s="5" t="n">
         <v>3.67</v>
       </c>
-      <c r="P131" s="5" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q131" s="5" t="n">
+      <c r="S131" s="5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T131" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="R131" s="5" t="inlineStr">
+      <c r="U131" s="5" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="3" t="n">
         <v>2170</v>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>target · asin="B072WT7WQ8"</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I132" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N132" s="2" t="n">
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M132" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N132" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P132" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q132" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O132" s="2" t="n">
+      <c r="R132" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P132" s="2" t="n">
+      <c r="S132" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q132" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R132" s="2" t="inlineStr">
+      <c r="T132" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U132" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="3" t="n">
         <v>2171</v>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>target · asin="B07MZ4GKZH"</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N133" s="2" t="n">
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N133" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q133" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O133" s="2" t="n">
+      <c r="R133" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P133" s="2" t="n">
+      <c r="S133" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q133" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R133" s="2" t="inlineStr">
+      <c r="T133" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U133" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="3" t="n">
         <v>2172</v>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>target · asin="B07YKCZHGK"</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M134" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N134" s="2" t="n">
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M134" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N134" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P134" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q134" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O134" s="2" t="n">
+      <c r="R134" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P134" s="2" t="n">
+      <c r="S134" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q134" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R134" s="2" t="inlineStr">
+      <c r="T134" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U134" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="3" t="n">
         <v>2173</v>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>target · asin="B09P86HJSV"</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N135" s="2" t="n">
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P135" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q135" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O135" s="2" t="n">
+      <c r="R135" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P135" s="2" t="n">
+      <c r="S135" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q135" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R135" s="2" t="inlineStr">
+      <c r="T135" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U135" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>target · asin="B09PYKYCCF"</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M136" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N136" s="2" t="n">
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M136" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N136" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P136" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q136" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O136" s="2" t="n">
+      <c r="R136" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P136" s="2" t="n">
+      <c r="S136" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q136" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R136" s="2" t="inlineStr">
+      <c r="T136" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U136" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="3" t="n">
         <v>2175</v>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>target · asin="B0BGSWNXQ8"</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M137" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N137" s="2" t="n">
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M137" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N137" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P137" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q137" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O137" s="2" t="n">
+      <c r="R137" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P137" s="2" t="n">
+      <c r="S137" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q137" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R137" s="2" t="inlineStr">
+      <c r="T137" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U137" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="3" t="n">
         <v>2176</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>DBS4-SP-B07YKCZHGK-(PAT)-Targeting-(Conversion)-DO-BAMBOO-KING-CREME</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>510977750871435</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>target · asin="B0BR53P7DY"</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>27/6/166</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M138" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N138" s="2" t="n">
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>27/7/183</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="M138" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N138" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="P138" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q138" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="O138" s="2" t="n">
+      <c r="R138" s="3" t="n">
         <v>1.83</v>
       </c>
-      <c r="P138" s="2" t="n">
+      <c r="S138" s="3" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q138" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
+      <c r="T138" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U138" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -11101,28 +12304,37 @@
       </c>
       <c r="K139" s="3" t="inlineStr">
         <is>
-          <t>388/186/559</t>
+          <t>389/192/562</t>
         </is>
       </c>
       <c r="L139" s="3" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="O139" s="3" t="n">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="P139" s="3" t="n">
-        <v>1.6</v>
+        <v>3.27</v>
       </c>
       <c r="Q139" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="R139" s="3" t="inlineStr">
+      <c r="R139" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S139" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T139" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U139" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -11179,106 +12391,124 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>388/186/559</t>
+          <t>389/192/562</t>
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="O140" s="3" t="n">
-        <v>1.44</v>
+        <v>0.5</v>
       </c>
       <c r="P140" s="3" t="n">
-        <v>1.6</v>
+        <v>3.27</v>
       </c>
       <c r="Q140" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="R140" s="3" t="inlineStr">
+      <c r="R140" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S140" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T140" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U140" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
+      <c r="A141" s="4" t="n">
         <v>2179</v>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>DBS4-SP-CATEGORY=BEDDING SHEETS &amp; PILLOWCASES-(PAT)-Targeting-(Conversion)-DO-BAMBOO-QUEEN-OLIVE</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>165947249807233</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
         <is>
           <t>target · category="Bedding Sheets &amp; Pillowcases"</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F141" s="4" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G141" s="4" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
         <is>
           <t>DEAL</t>
         </is>
       </c>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t>1/4/8</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="M141" s="3" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N141" s="3" t="n">
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>1/4/24</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="M141" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="4" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="P141" s="4" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="Q141" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="O141" s="3" t="n">
+      <c r="R141" s="4" t="n">
         <v>2.25</v>
       </c>
-      <c r="P141" s="3" t="n">
+      <c r="S141" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q141" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R141" s="3" t="inlineStr">
+      <c r="T141" s="4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U141" s="4" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -11335,18 +12565,29 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L142" s="3" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M142" s="3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N142" s="3" t="n"/>
-      <c r="O142" s="3" t="n"/>
-      <c r="P142" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N142" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="3" t="n">
+        <v>4.3</v>
+      </c>
       <c r="Q142" s="3" t="n"/>
-      <c r="R142" s="3" t="inlineStr"/>
+      <c r="R142" s="3" t="n"/>
+      <c r="S142" s="3" t="n"/>
+      <c r="T142" s="3" t="n"/>
+      <c r="U142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
@@ -11402,21 +12643,28 @@
         <v>0.429</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O143" s="3" t="n">
-        <v>1.71</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O143" s="3" t="n"/>
       <c r="P143" s="3" t="n">
-        <v>1.9</v>
+        <v>4.06</v>
       </c>
       <c r="Q143" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R143" s="3" t="inlineStr">
+      <c r="R143" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S143" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T143" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U143" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -11476,21 +12724,28 @@
         <v>0.429</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O144" s="3" t="n">
-        <v>1.71</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O144" s="3" t="n"/>
       <c r="P144" s="3" t="n">
-        <v>1.9</v>
+        <v>4.06</v>
       </c>
       <c r="Q144" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="R144" s="3" t="inlineStr">
+      <c r="R144" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S144" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T144" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U144" s="3" t="inlineStr">
         <is>
           <t>price held — inside its ceiling; the objective is governed outside this document</t>
         </is>
@@ -11547,86 +12802,104 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>291/4/186</t>
+          <t>393/5/195</t>
         </is>
       </c>
       <c r="L145" s="6" t="n">
         <v>0.008</v>
       </c>
       <c r="M145" s="6" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="N145" s="6" t="n"/>
-      <c r="O145" s="6" t="n"/>
-      <c r="P145" s="6" t="n"/>
+        <v>8.6</v>
+      </c>
+      <c r="N145" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="O145" s="6" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="P145" s="6" t="n">
+        <v>7.58</v>
+      </c>
       <c r="Q145" s="6" t="n"/>
-      <c r="R145" s="6" t="inlineStr"/>
+      <c r="R145" s="6" t="n"/>
+      <c r="S145" s="6" t="n"/>
+      <c r="T145" s="6" t="n"/>
+      <c r="U145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="n">
+      <c r="A146" s="6" t="n">
         <v>2303</v>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>DBS4-SP-100 Bamboo-(VLSV)-Broad-(Discovery)-DO-BAMBOO-QUEEN-WHITE</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>332114561773037</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>tos</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G146" s="4" t="inlineStr">
+      <c r="G146" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr">
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>DEAL</t>
-        </is>
-      </c>
-      <c r="K146" s="4" t="inlineStr">
-        <is>
-          <t>19/47/149</t>
-        </is>
-      </c>
-      <c r="L146" s="4" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="M146" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N146" s="4" t="n"/>
-      <c r="O146" s="4" t="n"/>
-      <c r="P146" s="4" t="n"/>
-      <c r="Q146" s="4" t="n"/>
-      <c r="R146" s="4" t="inlineStr"/>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>NONRANK-TOS-CUT, DEAL</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>27/63/165</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="M146" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N146" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O146" s="6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P146" s="6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="Q146" s="6" t="n"/>
+      <c r="R146" s="6" t="n"/>
+      <c r="S146" s="6" t="n"/>
+      <c r="T146" s="6" t="n"/>
+      <c r="U146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -11668,7 +12941,7 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11677,28 +12950,37 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>5/7/0</t>
+          <t>7/28/0</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>0.583</v>
+        <v>0.8</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4.53</v>
+        <v>0.2</v>
       </c>
       <c r="N147" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O147" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P147" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q147" s="2" t="n">
         <v>4.95</v>
       </c>
-      <c r="O147" s="2" t="n">
+      <c r="R147" s="2" t="n">
         <v>3.09</v>
       </c>
-      <c r="P147" s="2" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q147" s="2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R147" s="2" t="inlineStr">
+      <c r="S147" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T147" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U147" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -11744,7 +13026,7 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11753,28 +13035,37 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>10/0/2</t>
+          <t>13/3/9</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4.78</v>
+        <v>0.3</v>
       </c>
       <c r="N148" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O148" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P148" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="Q148" s="2" t="n">
         <v>5.43</v>
       </c>
-      <c r="O148" s="2" t="n">
+      <c r="R148" s="2" t="n">
         <v>3.67</v>
       </c>
-      <c r="P148" s="2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="Q148" s="2" t="n">
+      <c r="S148" s="2" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="T148" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R148" s="2" t="inlineStr">
+      <c r="U148" s="2" t="inlineStr">
         <is>
           <t>descent to a named point: the TOS ceiling (non-ranking objective — bounded at every placement)</t>
         </is>
@@ -11831,20 +13122,29 @@
       </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>1/3/0</t>
+          <t>4/10/0</t>
         </is>
       </c>
       <c r="L149" s="4" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="M149" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N149" s="4" t="n"/>
-      <c r="O149" s="4" t="n"/>
-      <c r="P149" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N149" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O149" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P149" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q149" s="4" t="n"/>
-      <c r="R149" s="4" t="inlineStr"/>
+      <c r="R149" s="4" t="n"/>
+      <c r="S149" s="4" t="n"/>
+      <c r="T149" s="4" t="n"/>
+      <c r="U149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="n">
@@ -11897,20 +13197,29 @@
       </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>3/3/2</t>
         </is>
       </c>
       <c r="L150" s="4" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="M150" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N150" s="4" t="n"/>
-      <c r="O150" s="4" t="n"/>
-      <c r="P150" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N150" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O150" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P150" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q150" s="4" t="n"/>
-      <c r="R150" s="4" t="inlineStr"/>
+      <c r="R150" s="4" t="n"/>
+      <c r="S150" s="4" t="n"/>
+      <c r="T150" s="4" t="n"/>
+      <c r="U150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -11963,18 +13272,29 @@
       </c>
       <c r="K151" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L151" s="4" t="n"/>
+          <t>0/6/0</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M151" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N151" s="4" t="n"/>
-      <c r="O151" s="4" t="n"/>
-      <c r="P151" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N151" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q151" s="4" t="n"/>
-      <c r="R151" s="4" t="inlineStr"/>
+      <c r="R151" s="4" t="n"/>
+      <c r="S151" s="4" t="n"/>
+      <c r="T151" s="4" t="n"/>
+      <c r="U151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -12027,18 +13347,29 @@
       </c>
       <c r="K152" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L152" s="4" t="n"/>
+          <t>3/0/0</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M152" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N152" s="4" t="n"/>
-      <c r="O152" s="4" t="n"/>
-      <c r="P152" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N152" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O152" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P152" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q152" s="4" t="n"/>
-      <c r="R152" s="4" t="inlineStr"/>
+      <c r="R152" s="4" t="n"/>
+      <c r="S152" s="4" t="n"/>
+      <c r="T152" s="4" t="n"/>
+      <c r="U152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -12091,18 +13422,29 @@
       </c>
       <c r="K153" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="n"/>
+          <t>2/0/0</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M153" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N153" s="4" t="n"/>
-      <c r="O153" s="4" t="n"/>
-      <c r="P153" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N153" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q153" s="4" t="n"/>
-      <c r="R153" s="4" t="inlineStr"/>
+      <c r="R153" s="4" t="n"/>
+      <c r="S153" s="4" t="n"/>
+      <c r="T153" s="4" t="n"/>
+      <c r="U153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n">
@@ -12155,20 +13497,29 @@
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>1/0/0</t>
+          <t>2/0/0</t>
         </is>
       </c>
       <c r="L154" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M154" s="6" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="N154" s="6" t="n"/>
-      <c r="O154" s="6" t="n"/>
-      <c r="P154" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N154" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O154" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="6" t="n">
+        <v>4.83</v>
+      </c>
       <c r="Q154" s="6" t="n"/>
-      <c r="R154" s="6" t="inlineStr"/>
+      <c r="R154" s="6" t="n"/>
+      <c r="S154" s="6" t="n"/>
+      <c r="T154" s="6" t="n"/>
+      <c r="U154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
@@ -12221,18 +13572,29 @@
       </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L155" s="4" t="n"/>
+          <t>1/2/0</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="n">
+        <v>0.667</v>
+      </c>
       <c r="M155" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N155" s="4" t="n"/>
-      <c r="O155" s="4" t="n"/>
-      <c r="P155" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N155" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O155" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P155" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q155" s="4" t="n"/>
-      <c r="R155" s="4" t="inlineStr"/>
+      <c r="R155" s="4" t="n"/>
+      <c r="S155" s="4" t="n"/>
+      <c r="T155" s="4" t="n"/>
+      <c r="U155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
@@ -12285,18 +13647,29 @@
       </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L156" s="4" t="n"/>
+          <t>1/1/1</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="n">
+        <v>0.333</v>
+      </c>
       <c r="M156" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N156" s="4" t="n"/>
-      <c r="O156" s="4" t="n"/>
-      <c r="P156" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N156" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O156" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P156" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q156" s="4" t="n"/>
-      <c r="R156" s="4" t="inlineStr"/>
+      <c r="R156" s="4" t="n"/>
+      <c r="S156" s="4" t="n"/>
+      <c r="T156" s="4" t="n"/>
+      <c r="U156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n">
@@ -12349,20 +13722,29 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>278/111/779</t>
+          <t>280/111/781</t>
         </is>
       </c>
       <c r="L157" s="6" t="n">
         <v>0.095</v>
       </c>
       <c r="M157" s="6" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="N157" s="6" t="n"/>
-      <c r="O157" s="6" t="n"/>
-      <c r="P157" s="6" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="N157" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O157" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P157" s="6" t="n">
+        <v>4.45</v>
+      </c>
       <c r="Q157" s="6" t="n"/>
-      <c r="R157" s="6" t="inlineStr"/>
+      <c r="R157" s="6" t="n"/>
+      <c r="S157" s="6" t="n"/>
+      <c r="T157" s="6" t="n"/>
+      <c r="U157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n">
@@ -12415,20 +13797,29 @@
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>0/0/1</t>
+          <t>0/0/2</t>
         </is>
       </c>
       <c r="L158" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N158" s="6" t="n"/>
-      <c r="O158" s="6" t="n"/>
-      <c r="P158" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="6" t="n">
+        <v>4.47</v>
+      </c>
       <c r="Q158" s="6" t="n"/>
-      <c r="R158" s="6" t="inlineStr"/>
+      <c r="R158" s="6" t="n"/>
+      <c r="S158" s="6" t="n"/>
+      <c r="T158" s="6" t="n"/>
+      <c r="U158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n">
@@ -12481,18 +13872,29 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L159" s="6" t="n"/>
+          <t>2/0/0</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="M159" s="6" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="N159" s="6" t="n"/>
-      <c r="O159" s="6" t="n"/>
-      <c r="P159" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N159" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" s="6" t="n">
+        <v>4.83</v>
+      </c>
       <c r="Q159" s="6" t="n"/>
-      <c r="R159" s="6" t="inlineStr"/>
+      <c r="R159" s="6" t="n"/>
+      <c r="S159" s="6" t="n"/>
+      <c r="T159" s="6" t="n"/>
+      <c r="U159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n">
@@ -12545,18 +13947,29 @@
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L160" s="6" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="M160" s="6" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="N160" s="6" t="n"/>
-      <c r="O160" s="6" t="n"/>
-      <c r="P160" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N160" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O160" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="6" t="n">
+        <v>4.83</v>
+      </c>
       <c r="Q160" s="6" t="n"/>
-      <c r="R160" s="6" t="inlineStr"/>
+      <c r="R160" s="6" t="n"/>
+      <c r="S160" s="6" t="n"/>
+      <c r="T160" s="6" t="n"/>
+      <c r="U160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n">
@@ -12616,13 +14029,20 @@
         <v>0</v>
       </c>
       <c r="M161" s="6" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="N161" s="6" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N161" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="O161" s="6" t="n"/>
-      <c r="P161" s="6" t="n"/>
+      <c r="P161" s="6" t="n">
+        <v>4.83</v>
+      </c>
       <c r="Q161" s="6" t="n"/>
-      <c r="R161" s="6" t="inlineStr"/>
+      <c r="R161" s="6" t="n"/>
+      <c r="S161" s="6" t="n"/>
+      <c r="T161" s="6" t="n"/>
+      <c r="U161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n">
@@ -12675,18 +14095,29 @@
       </c>
       <c r="K162" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L162" s="4" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M162" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N162" s="4" t="n"/>
-      <c r="O162" s="4" t="n"/>
-      <c r="P162" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N162" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O162" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q162" s="4" t="n"/>
-      <c r="R162" s="4" t="inlineStr"/>
+      <c r="R162" s="4" t="n"/>
+      <c r="S162" s="4" t="n"/>
+      <c r="T162" s="4" t="n"/>
+      <c r="U162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -12739,18 +14170,29 @@
       </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L163" s="4" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M163" s="4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N163" s="4" t="n"/>
-      <c r="O163" s="4" t="n"/>
-      <c r="P163" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N163" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O163" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="4" t="n">
+        <v>4.3</v>
+      </c>
       <c r="Q163" s="4" t="n"/>
-      <c r="R163" s="4" t="inlineStr"/>
+      <c r="R163" s="4" t="n"/>
+      <c r="S163" s="4" t="n"/>
+      <c r="T163" s="4" t="n"/>
+      <c r="U163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
@@ -12806,13 +14248,20 @@
         <v>0</v>
       </c>
       <c r="M164" s="4" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="N164" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N164" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O164" s="4" t="n"/>
-      <c r="P164" s="4" t="n"/>
+      <c r="P164" s="4" t="n">
+        <v>4.06</v>
+      </c>
       <c r="Q164" s="4" t="n"/>
-      <c r="R164" s="4" t="inlineStr"/>
+      <c r="R164" s="4" t="n"/>
+      <c r="S164" s="4" t="n"/>
+      <c r="T164" s="4" t="n"/>
+      <c r="U164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -12865,18 +14314,29 @@
       </c>
       <c r="K165" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L165" s="4" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M165" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N165" s="4" t="n"/>
-      <c r="O165" s="4" t="n"/>
-      <c r="P165" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N165" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q165" s="4" t="n"/>
-      <c r="R165" s="4" t="inlineStr"/>
+      <c r="R165" s="4" t="n"/>
+      <c r="S165" s="4" t="n"/>
+      <c r="T165" s="4" t="n"/>
+      <c r="U165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -12929,18 +14389,29 @@
       </c>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L166" s="4" t="n"/>
+          <t>1/0/0</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M166" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N166" s="4" t="n"/>
-      <c r="O166" s="4" t="n"/>
-      <c r="P166" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N166" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q166" s="4" t="n"/>
-      <c r="R166" s="4" t="inlineStr"/>
+      <c r="R166" s="4" t="n"/>
+      <c r="S166" s="4" t="n"/>
+      <c r="T166" s="4" t="n"/>
+      <c r="U166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -12993,18 +14464,29 @@
       </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L167" s="4" t="n"/>
+          <t>0/2/0</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M167" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N167" s="4" t="n"/>
-      <c r="O167" s="4" t="n"/>
-      <c r="P167" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N167" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="4" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="P167" s="4" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q167" s="4" t="n"/>
-      <c r="R167" s="4" t="inlineStr"/>
+      <c r="R167" s="4" t="n"/>
+      <c r="S167" s="4" t="n"/>
+      <c r="T167" s="4" t="n"/>
+      <c r="U167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
@@ -13057,18 +14539,29 @@
       </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L168" s="4" t="n"/>
+          <t>0/0/1</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="M168" s="4" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N168" s="4" t="n"/>
-      <c r="O168" s="4" t="n"/>
-      <c r="P168" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" s="4" t="n">
+        <v>4.5</v>
+      </c>
       <c r="Q168" s="4" t="n"/>
-      <c r="R168" s="4" t="inlineStr"/>
+      <c r="R168" s="4" t="n"/>
+      <c r="S168" s="4" t="n"/>
+      <c r="T168" s="4" t="n"/>
+      <c r="U168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -13121,18 +14614,29 @@
       </c>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>0/0/0</t>
-        </is>
-      </c>
-      <c r="L169" s="4" t="n"/>
+          <t>1/1/0</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M169" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N169" s="4" t="n"/>
-      <c r="O169" s="4" t="n"/>
-      <c r="P169" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N169" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O169" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P169" s="4" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q169" s="4" t="n"/>
-      <c r="R169" s="4" t="inlineStr"/>
+      <c r="R169" s="4" t="n"/>
+      <c r="S169" s="4" t="n"/>
+      <c r="T169" s="4" t="n"/>
+      <c r="U169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
@@ -13186,13 +14690,20 @@
       </c>
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="N170" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N170" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O170" s="4" t="n"/>
-      <c r="P170" s="4" t="n"/>
+      <c r="P170" s="4" t="n">
+        <v>4.13</v>
+      </c>
       <c r="Q170" s="4" t="n"/>
-      <c r="R170" s="4" t="inlineStr"/>
+      <c r="R170" s="4" t="n"/>
+      <c r="S170" s="4" t="n"/>
+      <c r="T170" s="4" t="n"/>
+      <c r="U170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -13248,13 +14759,20 @@
         <v>0</v>
       </c>
       <c r="M171" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N171" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N171" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O171" s="4" t="n"/>
-      <c r="P171" s="4" t="n"/>
+      <c r="P171" s="4" t="n">
+        <v>3.87</v>
+      </c>
       <c r="Q171" s="4" t="n"/>
-      <c r="R171" s="4" t="inlineStr"/>
+      <c r="R171" s="4" t="n"/>
+      <c r="S171" s="4" t="n"/>
+      <c r="T171" s="4" t="n"/>
+      <c r="U171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -13310,13 +14828,20 @@
         <v>0.667</v>
       </c>
       <c r="M172" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N172" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N172" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O172" s="4" t="n"/>
-      <c r="P172" s="4" t="n"/>
+      <c r="P172" s="4" t="n">
+        <v>4.48</v>
+      </c>
       <c r="Q172" s="4" t="n"/>
-      <c r="R172" s="4" t="inlineStr"/>
+      <c r="R172" s="4" t="n"/>
+      <c r="S172" s="4" t="n"/>
+      <c r="T172" s="4" t="n"/>
+      <c r="U172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -13372,13 +14897,20 @@
         <v>0</v>
       </c>
       <c r="M173" s="4" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="N173" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N173" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O173" s="4" t="n"/>
-      <c r="P173" s="4" t="n"/>
+      <c r="P173" s="4" t="n">
+        <v>4.74</v>
+      </c>
       <c r="Q173" s="4" t="n"/>
-      <c r="R173" s="4" t="inlineStr"/>
+      <c r="R173" s="4" t="n"/>
+      <c r="S173" s="4" t="n"/>
+      <c r="T173" s="4" t="n"/>
+      <c r="U173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
@@ -13434,13 +14966,20 @@
         <v>0.5</v>
       </c>
       <c r="M174" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="N174" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N174" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O174" s="4" t="n"/>
-      <c r="P174" s="4" t="n"/>
+      <c r="P174" s="4" t="n">
+        <v>3.87</v>
+      </c>
       <c r="Q174" s="4" t="n"/>
-      <c r="R174" s="4" t="inlineStr"/>
+      <c r="R174" s="4" t="n"/>
+      <c r="S174" s="4" t="n"/>
+      <c r="T174" s="4" t="n"/>
+      <c r="U174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -13496,13 +15035,20 @@
         <v>0</v>
       </c>
       <c r="M175" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N175" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N175" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O175" s="4" t="n"/>
-      <c r="P175" s="4" t="n"/>
+      <c r="P175" s="4" t="n">
+        <v>4.48</v>
+      </c>
       <c r="Q175" s="4" t="n"/>
-      <c r="R175" s="4" t="inlineStr"/>
+      <c r="R175" s="4" t="n"/>
+      <c r="S175" s="4" t="n"/>
+      <c r="T175" s="4" t="n"/>
+      <c r="U175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
@@ -13556,16 +15102,23 @@
       </c>
       <c r="L176" s="4" t="n"/>
       <c r="M176" s="4" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="N176" s="4" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="N176" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="O176" s="4" t="n"/>
-      <c r="P176" s="4" t="n"/>
+      <c r="P176" s="4" t="n">
+        <v>4.06</v>
+      </c>
       <c r="Q176" s="4" t="n"/>
-      <c r="R176" s="4" t="inlineStr"/>
+      <c r="R176" s="4" t="n"/>
+      <c r="S176" s="4" t="n"/>
+      <c r="T176" s="4" t="n"/>
+      <c r="U176" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R176"/>
+  <autoFilter ref="A1:U176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>